--- a/exports/RANKING_trend_following.xlsx
+++ b/exports/RANKING_trend_following.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J203"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,79 +471,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>FINNIFTY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.33pp)</t>
-        </is>
-      </c>
+        <v>93.2</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>69.2</v>
+        <v>55.3</v>
       </c>
       <c r="H2" t="n">
-        <v>12.12</v>
+        <v>2.14</v>
       </c>
       <c r="I2" t="n">
-        <v>7.79</v>
+        <v>0.54</v>
       </c>
       <c r="J2" t="n">
-        <v>3.72</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>MIDCPNIFTY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.44pp)</t>
-        </is>
-      </c>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>51.1</v>
       </c>
       <c r="H3" t="n">
-        <v>8.01</v>
+        <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>4.57</v>
+        <v>0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.31</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,30 +544,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>91.5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.65pp)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>63.2</v>
+        <v>61.1</v>
       </c>
       <c r="H4" t="n">
-        <v>4.19</v>
+        <v>6.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,34 +580,30 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.30pp)</t>
-        </is>
-      </c>
+        <v>89.5</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>63.9</v>
+        <v>56.2</v>
       </c>
       <c r="H5" t="n">
-        <v>9.56</v>
+        <v>4.57</v>
       </c>
       <c r="I5" t="n">
-        <v>5.26</v>
+        <v>1.64</v>
       </c>
       <c r="J5" t="n">
-        <v>3.73</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,98 +612,102 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.33pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.58pp)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>65.7</v>
+        <v>59</v>
       </c>
       <c r="H6" t="n">
-        <v>6.74</v>
+        <v>7.43</v>
       </c>
       <c r="I6" t="n">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="J6" t="n">
-        <v>3.72</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>NIFTY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>65.59999999999999</v>
+        <v>46.8</v>
       </c>
       <c r="H7" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="I7" t="n">
-        <v>4.54</v>
+        <v>-0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>4.74</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MIDCPNIFTY</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.23pp)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>66.3</v>
+        <v>48.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="I8" t="n">
-        <v>1.99</v>
+        <v>-0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -720,30 +716,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.80pp)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>63.4</v>
+        <v>48.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.45</v>
+        <v>3.72</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>-0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -752,34 +752,30 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.57pp)</t>
-        </is>
-      </c>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>80</v>
+        <v>52.5</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.43</v>
+        <v>0.34</v>
       </c>
       <c r="J10" t="n">
-        <v>5.05</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -788,98 +784,98 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>81.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>64.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="H11" t="n">
-        <v>4.65</v>
+        <v>2.46</v>
       </c>
       <c r="I11" t="n">
-        <v>2.04</v>
+        <v>-0.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.19pp)</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>61.7</v>
+        <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>4.05</v>
+        <v>6.07</v>
       </c>
       <c r="I12" t="n">
-        <v>1.84</v>
+        <v>0.88</v>
       </c>
       <c r="J12" t="n">
-        <v>1.98</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SENSEX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.62pp)</t>
-        </is>
-      </c>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>64.09999999999999</v>
+        <v>44</v>
       </c>
       <c r="H13" t="n">
-        <v>9.31</v>
+        <v>1.47</v>
       </c>
       <c r="I13" t="n">
-        <v>3.69</v>
+        <v>-0.43</v>
       </c>
       <c r="J13" t="n">
-        <v>4.47</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -888,34 +884,30 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.22pp)</t>
-        </is>
-      </c>
+        <v>82.2</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>45.9</v>
       </c>
       <c r="H14" t="n">
-        <v>5.54</v>
+        <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>2.32</v>
+        <v>-0.63</v>
       </c>
       <c r="J14" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -924,34 +916,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>78.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.96pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.20pp)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>63.2</v>
+        <v>46.9</v>
       </c>
       <c r="H15" t="n">
-        <v>9.25</v>
+        <v>2.66</v>
       </c>
       <c r="I15" t="n">
-        <v>4.29</v>
+        <v>-0.54</v>
       </c>
       <c r="J15" t="n">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -960,30 +952,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.17pp)</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>59.4</v>
+        <v>54.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.85</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -992,34 +988,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>78.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.48pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.46pp)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>53.8</v>
       </c>
       <c r="H17" t="n">
-        <v>6.44</v>
+        <v>7.17</v>
       </c>
       <c r="I17" t="n">
-        <v>2.96</v>
+        <v>1.71</v>
       </c>
       <c r="J17" t="n">
-        <v>4.28</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1028,66 +1024,66 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>77</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.45pp)</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>61.9</v>
+        <v>48.6</v>
       </c>
       <c r="H18" t="n">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="I18" t="n">
-        <v>1.66</v>
+        <v>-0.47</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>77</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.03pp)</t>
-        </is>
-      </c>
+        <v>79.5</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>57.5</v>
+        <v>44.7</v>
       </c>
       <c r="H19" t="n">
-        <v>8.15</v>
+        <v>1.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.12</v>
+        <v>-0.91</v>
       </c>
       <c r="J19" t="n">
-        <v>5.52</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1096,70 +1092,66 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.85pp)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+        <v>78.90000000000001</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>68.59999999999999</v>
+        <v>48.6</v>
       </c>
       <c r="H20" t="n">
-        <v>15.61</v>
+        <v>1.93</v>
       </c>
       <c r="I20" t="n">
-        <v>5.76</v>
+        <v>-0.97</v>
       </c>
       <c r="J20" t="n">
-        <v>4.81</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>78.59999999999999</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.38pp)</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>59.6</v>
+        <v>56.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3.37</v>
+        <v>12.17</v>
       </c>
       <c r="I21" t="n">
-        <v>1.27</v>
+        <v>0.79</v>
       </c>
       <c r="J21" t="n">
-        <v>1.35</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1168,34 +1160,38 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>75.5</v>
+        <v>78.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.29pp)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.14pp)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H22" t="n">
-        <v>12.43</v>
+        <v>4.92</v>
       </c>
       <c r="I22" t="n">
-        <v>4.14</v>
+        <v>-0.22</v>
       </c>
       <c r="J22" t="n">
-        <v>3.28</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1204,70 +1200,66 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.14pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.13pp)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>62.5</v>
+        <v>43.6</v>
       </c>
       <c r="H23" t="n">
-        <v>6.06</v>
+        <v>2.37</v>
       </c>
       <c r="I23" t="n">
-        <v>2.92</v>
+        <v>-0.76</v>
       </c>
       <c r="J23" t="n">
-        <v>5.3</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NIFTYNXT50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 12.58pp)</t>
-        </is>
-      </c>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>65.2</v>
+        <v>42.3</v>
       </c>
       <c r="H24" t="n">
-        <v>16.4</v>
+        <v>2.07</v>
       </c>
       <c r="I24" t="n">
-        <v>3.82</v>
+        <v>-0.68</v>
       </c>
       <c r="J24" t="n">
-        <v>3.74</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1276,70 +1268,74 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.23pp)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.83pp)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="H25" t="n">
-        <v>16.07</v>
+        <v>7.18</v>
       </c>
       <c r="I25" t="n">
-        <v>8.84</v>
+        <v>1.35</v>
       </c>
       <c r="J25" t="n">
-        <v>6.56</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SENSEX</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+        <v>77.3</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.09pp)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F26" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
       </c>
       <c r="H26" t="n">
-        <v>2.91</v>
+        <v>11.9</v>
       </c>
       <c r="I26" t="n">
-        <v>0.97</v>
+        <v>5.81</v>
       </c>
       <c r="J26" t="n">
-        <v>1.56</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1348,34 +1344,38 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>74.5</v>
+        <v>77.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.04pp)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.71pp)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="H27" t="n">
-        <v>6.23</v>
+        <v>10.92</v>
       </c>
       <c r="I27" t="n">
-        <v>2.19</v>
+        <v>6.21</v>
       </c>
       <c r="J27" t="n">
-        <v>3.46</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1384,30 +1384,34 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>77.3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.32pp)</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>63.6</v>
+        <v>46.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.36</v>
+        <v>2.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>-0.82</v>
       </c>
       <c r="J28" t="n">
-        <v>4.64</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1416,34 +1420,38 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.07pp)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.83pp)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G29" t="n">
-        <v>71.8</v>
+        <v>51.7</v>
       </c>
       <c r="H29" t="n">
-        <v>12.71</v>
+        <v>7.12</v>
       </c>
       <c r="I29" t="n">
-        <v>4.64</v>
+        <v>0.29</v>
       </c>
       <c r="J29" t="n">
-        <v>5.46</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1452,34 +1460,30 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.05pp)</t>
-        </is>
-      </c>
+        <v>76.5</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>57.1</v>
+        <v>42.1</v>
       </c>
       <c r="H30" t="n">
-        <v>6.46</v>
+        <v>1.96</v>
       </c>
       <c r="I30" t="n">
-        <v>2.41</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1488,32 +1492,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>73.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.08pp)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.00pp)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>71</v>
+        <v>47.4</v>
       </c>
       <c r="H31" t="n">
-        <v>15.4</v>
+        <v>4.87</v>
       </c>
       <c r="I31" t="n">
-        <v>9.32</v>
+        <v>-0.13</v>
       </c>
       <c r="J31" t="n">
-        <v>8.08</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="32">
@@ -1528,11 +1528,11 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>72.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.35pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.00pp)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1540,58 +1540,62 @@
         <v>31</v>
       </c>
       <c r="G32" t="n">
-        <v>67.7</v>
+        <v>48.4</v>
       </c>
       <c r="H32" t="n">
-        <v>7.19</v>
+        <v>3.98</v>
       </c>
       <c r="I32" t="n">
-        <v>2.84</v>
+        <v>-0.02</v>
       </c>
       <c r="J32" t="n">
-        <v>5.65</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NIFTYNXT50</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>72.3</v>
+        <v>74.3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.16pp)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.53pp)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F33" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="G33" t="n">
-        <v>61.5</v>
+        <v>56.7</v>
       </c>
       <c r="H33" t="n">
-        <v>4.08</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="J33" t="n">
-        <v>1.6</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,34 +1604,38 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>72.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.61pp)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.56pp)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F34" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G34" t="n">
-        <v>61.8</v>
+        <v>54.3</v>
       </c>
       <c r="H34" t="n">
-        <v>8.949999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="I34" t="n">
-        <v>3.34</v>
+        <v>0.58</v>
       </c>
       <c r="J34" t="n">
-        <v>5.14</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1636,34 +1644,34 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>72.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.58pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.75pp)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>55.8</v>
+        <v>60</v>
       </c>
       <c r="H35" t="n">
-        <v>8.24</v>
+        <v>7.53</v>
       </c>
       <c r="I35" t="n">
-        <v>3.66</v>
+        <v>0.78</v>
       </c>
       <c r="J35" t="n">
-        <v>4.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1672,34 +1680,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>72</v>
+        <v>73.8</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.44pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.36pp)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>56.7</v>
+        <v>56</v>
       </c>
       <c r="H36" t="n">
-        <v>10.96</v>
+        <v>6.52</v>
       </c>
       <c r="I36" t="n">
-        <v>7.52</v>
+        <v>1.16</v>
       </c>
       <c r="J36" t="n">
-        <v>6.62</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1708,34 +1716,34 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>71.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.57pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.36pp)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>64.90000000000001</v>
+        <v>46.9</v>
       </c>
       <c r="H37" t="n">
-        <v>11.24</v>
+        <v>4.64</v>
       </c>
       <c r="I37" t="n">
-        <v>3.67</v>
+        <v>-0.72</v>
       </c>
       <c r="J37" t="n">
-        <v>5.22</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1744,30 +1752,34 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.89pp)</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G38" t="n">
-        <v>54.3</v>
+        <v>50</v>
       </c>
       <c r="H38" t="n">
-        <v>4.27</v>
+        <v>10.85</v>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>0.96</v>
       </c>
       <c r="J38" t="n">
-        <v>4.65</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1776,34 +1788,34 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>71</v>
+        <v>72.2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.55pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.89pp)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G39" t="n">
-        <v>72</v>
+        <v>51.4</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>6.87</v>
       </c>
       <c r="I39" t="n">
-        <v>3.45</v>
+        <v>0.98</v>
       </c>
       <c r="J39" t="n">
-        <v>5.32</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1812,34 +1824,34 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>70.3</v>
+        <v>72.2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.80pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.04pp)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G40" t="n">
-        <v>68</v>
+        <v>48.6</v>
       </c>
       <c r="H40" t="n">
-        <v>10.95</v>
+        <v>2.29</v>
       </c>
       <c r="I40" t="n">
-        <v>4.15</v>
+        <v>-1.75</v>
       </c>
       <c r="J40" t="n">
-        <v>6.47</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1848,28 +1860,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>70.2</v>
+        <v>72</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.51pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.79pp)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G41" t="n">
-        <v>56.8</v>
+        <v>60.7</v>
       </c>
       <c r="H41" t="n">
-        <v>5.09</v>
+        <v>12.65</v>
       </c>
       <c r="I41" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="J41" t="n">
-        <v>3.78</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="42">
@@ -1884,11 +1896,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>70</v>
+        <v>71.7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.49pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.88pp)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1896,22 +1908,22 @@
         <v>35</v>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="H42" t="n">
-        <v>5.81</v>
+        <v>2.59</v>
       </c>
       <c r="I42" t="n">
-        <v>1.32</v>
+        <v>-1.29</v>
       </c>
       <c r="J42" t="n">
-        <v>3.72</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1920,30 +1932,34 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.15pp)</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G43" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="H43" t="n">
-        <v>5.88</v>
+        <v>5.81</v>
       </c>
       <c r="I43" t="n">
-        <v>3.12</v>
+        <v>0.66</v>
       </c>
       <c r="J43" t="n">
-        <v>4.17</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1952,34 +1968,38 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>69.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.83pp)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 23.00pp)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F44" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G44" t="n">
-        <v>71.40000000000001</v>
+        <v>57.9</v>
       </c>
       <c r="H44" t="n">
-        <v>17.69</v>
+        <v>26.08</v>
       </c>
       <c r="I44" t="n">
-        <v>6.86</v>
+        <v>3.08</v>
       </c>
       <c r="J44" t="n">
-        <v>6.42</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1988,34 +2008,38 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>68.5</v>
+        <v>70.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.87pp)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.12pp)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>62.5</v>
+        <v>55</v>
       </c>
       <c r="H45" t="n">
-        <v>15.43</v>
+        <v>9.42</v>
       </c>
       <c r="I45" t="n">
-        <v>5.56</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
-        <v>5.63</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,38 +2048,34 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>68.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.26pp)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.03pp)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G46" t="n">
-        <v>70</v>
+        <v>42.9</v>
       </c>
       <c r="H46" t="n">
-        <v>16.2</v>
+        <v>1.54</v>
       </c>
       <c r="I46" t="n">
-        <v>7.94</v>
+        <v>-1.49</v>
       </c>
       <c r="J46" t="n">
-        <v>8.34</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2064,34 +2084,30 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.77pp)</t>
-        </is>
-      </c>
+        <v>70.5</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G47" t="n">
-        <v>56.4</v>
+        <v>39.5</v>
       </c>
       <c r="H47" t="n">
-        <v>4.93</v>
+        <v>0.49</v>
       </c>
       <c r="I47" t="n">
-        <v>1.16</v>
+        <v>-1.3</v>
       </c>
       <c r="J47" t="n">
-        <v>3.56</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2100,30 +2116,34 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+        <v>70.2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.96pp)</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G48" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="H48" t="n">
-        <v>3.54</v>
+        <v>4.01</v>
       </c>
       <c r="I48" t="n">
-        <v>1.35</v>
+        <v>-0.95</v>
       </c>
       <c r="J48" t="n">
-        <v>4.06</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2132,34 +2152,34 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>67.2</v>
+        <v>69.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.28pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.68pp)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G49" t="n">
-        <v>64</v>
+        <v>46.7</v>
       </c>
       <c r="H49" t="n">
-        <v>10.17</v>
+        <v>1.6</v>
       </c>
       <c r="I49" t="n">
-        <v>3.89</v>
+        <v>-2.08</v>
       </c>
       <c r="J49" t="n">
-        <v>7.09</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2168,34 +2188,34 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.03pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.48pp)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G50" t="n">
-        <v>56.4</v>
+        <v>40</v>
       </c>
       <c r="H50" t="n">
-        <v>6.02</v>
+        <v>2.59</v>
       </c>
       <c r="I50" t="n">
-        <v>2.99</v>
+        <v>-0.89</v>
       </c>
       <c r="J50" t="n">
-        <v>6.55</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2204,34 +2224,34 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>66.2</v>
+        <v>68.2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.20pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.12pp)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G51" t="n">
-        <v>62.1</v>
+        <v>43.6</v>
       </c>
       <c r="H51" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>-1.74</v>
       </c>
       <c r="J51" t="n">
-        <v>7.17</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2240,34 +2260,34 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>66.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.81pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.20pp)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G52" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="H52" t="n">
-        <v>7.67</v>
+        <v>5.29</v>
       </c>
       <c r="I52" t="n">
-        <v>1.86</v>
+        <v>-0.91</v>
       </c>
       <c r="J52" t="n">
-        <v>5.14</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2276,34 +2296,38 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>66</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.53pp)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.44pp)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F53" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G53" t="n">
-        <v>57.1</v>
+        <v>51.2</v>
       </c>
       <c r="H53" t="n">
-        <v>4.53</v>
+        <v>10.83</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="J53" t="n">
-        <v>4.16</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2312,34 +2336,34 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>65.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.85pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.94pp)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G54" t="n">
-        <v>62.2</v>
+        <v>55.6</v>
       </c>
       <c r="H54" t="n">
-        <v>6.64</v>
+        <v>12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.79</v>
+        <v>2.06</v>
       </c>
       <c r="J54" t="n">
-        <v>3.67</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2348,38 +2372,30 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 25.07pp)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+        <v>66.09999999999999</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G55" t="n">
-        <v>68.40000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="H55" t="n">
-        <v>29.72</v>
+        <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>4.65</v>
+        <v>-1.82</v>
       </c>
       <c r="J55" t="n">
-        <v>6.01</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2388,11 +2404,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>65.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 12.49pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.28pp)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2401,25 +2417,25 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G56" t="n">
-        <v>60</v>
+        <v>45.9</v>
       </c>
       <c r="H56" t="n">
-        <v>18.93</v>
+        <v>6.66</v>
       </c>
       <c r="I56" t="n">
-        <v>6.44</v>
+        <v>-0.62</v>
       </c>
       <c r="J56" t="n">
-        <v>5.72</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2428,38 +2444,30 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.15pp)</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G57" t="n">
-        <v>65.5</v>
+        <v>37.8</v>
       </c>
       <c r="H57" t="n">
-        <v>10.47</v>
+        <v>-0.41</v>
       </c>
       <c r="I57" t="n">
-        <v>2.32</v>
+        <v>-1.43</v>
       </c>
       <c r="J57" t="n">
-        <v>5.19</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2468,34 +2476,38 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>65.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.66pp)</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.93pp)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F58" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G58" t="n">
-        <v>65.90000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="H58" t="n">
-        <v>8.91</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>2.25</v>
+        <v>0.96</v>
       </c>
       <c r="J58" t="n">
-        <v>5.8</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2508,30 +2520,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.14pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.36pp)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G59" t="n">
-        <v>62.9</v>
+        <v>47.2</v>
       </c>
       <c r="H59" t="n">
-        <v>13.61</v>
+        <v>4.06</v>
       </c>
       <c r="I59" t="n">
-        <v>3.47</v>
+        <v>-1.3</v>
       </c>
       <c r="J59" t="n">
-        <v>5.5</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2540,30 +2552,34 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.86pp)</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G60" t="n">
-        <v>56.8</v>
+        <v>46.2</v>
       </c>
       <c r="H60" t="n">
-        <v>3.95</v>
+        <v>5.47</v>
       </c>
       <c r="I60" t="n">
-        <v>0.96</v>
+        <v>-1.39</v>
       </c>
       <c r="J60" t="n">
-        <v>4.76</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2572,38 +2588,34 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>63.9</v>
+        <v>64.5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.68pp)</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.30pp)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G61" t="n">
-        <v>63.2</v>
+        <v>41.5</v>
       </c>
       <c r="H61" t="n">
-        <v>13.84</v>
+        <v>2.29</v>
       </c>
       <c r="I61" t="n">
-        <v>3.16</v>
+        <v>-1.01</v>
       </c>
       <c r="J61" t="n">
-        <v>5.5</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2612,34 +2624,34 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>63.8</v>
+        <v>63.3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.26pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.70pp)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G62" t="n">
-        <v>60</v>
+        <v>38.9</v>
       </c>
       <c r="H62" t="n">
-        <v>13.42</v>
+        <v>3.95</v>
       </c>
       <c r="I62" t="n">
-        <v>4.16</v>
+        <v>-0.75</v>
       </c>
       <c r="J62" t="n">
-        <v>5.84</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2648,30 +2660,34 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+        <v>63.3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.21pp)</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G63" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="H63" t="n">
-        <v>2.11</v>
+        <v>15.92</v>
       </c>
       <c r="I63" t="n">
-        <v>1.52</v>
+        <v>0.71</v>
       </c>
       <c r="J63" t="n">
-        <v>4.12</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2680,34 +2696,34 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>63.1</v>
+        <v>63.3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.79pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.55pp)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G64" t="n">
-        <v>56.2</v>
+        <v>48.6</v>
       </c>
       <c r="H64" t="n">
-        <v>7.29</v>
+        <v>9.75</v>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>-0.8</v>
       </c>
       <c r="J64" t="n">
-        <v>5.5</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2718,32 +2734,28 @@
       <c r="C65" t="n">
         <v>62.9</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.48pp)</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G65" t="n">
-        <v>60</v>
+        <v>37.8</v>
       </c>
       <c r="H65" t="n">
-        <v>15.49</v>
+        <v>1.1</v>
       </c>
       <c r="I65" t="n">
-        <v>6.01</v>
+        <v>-1.1</v>
       </c>
       <c r="J65" t="n">
-        <v>7.04</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2752,34 +2764,30 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.56pp)</t>
-        </is>
-      </c>
+        <v>62.8</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G66" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="H66" t="n">
-        <v>17.92</v>
+        <v>0.05</v>
       </c>
       <c r="I66" t="n">
-        <v>9.359999999999999</v>
+        <v>-1.61</v>
       </c>
       <c r="J66" t="n">
-        <v>7.5</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2788,34 +2796,34 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.72pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.47pp)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G67" t="n">
-        <v>55.6</v>
+        <v>45</v>
       </c>
       <c r="H67" t="n">
-        <v>7.42</v>
+        <v>1.4</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>-2.07</v>
       </c>
       <c r="J67" t="n">
-        <v>4.52</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2824,30 +2832,34 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+        <v>61.8</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.31pp)</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G68" t="n">
-        <v>52.2</v>
+        <v>44</v>
       </c>
       <c r="H68" t="n">
-        <v>5.79</v>
+        <v>1.96</v>
       </c>
       <c r="I68" t="n">
-        <v>2.86</v>
+        <v>-2.35</v>
       </c>
       <c r="J68" t="n">
-        <v>5.34</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2856,34 +2868,34 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>61.9</v>
+        <v>61.4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.52pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.97pp)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G69" t="n">
-        <v>58.6</v>
+        <v>39.5</v>
       </c>
       <c r="H69" t="n">
-        <v>5.51</v>
+        <v>3.35</v>
       </c>
       <c r="I69" t="n">
-        <v>1.99</v>
+        <v>-1.62</v>
       </c>
       <c r="J69" t="n">
-        <v>6.65</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2892,28 +2904,32 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.15pp)</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 13.55pp)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G70" t="n">
-        <v>55.8</v>
+        <v>50</v>
       </c>
       <c r="H70" t="n">
-        <v>5.94</v>
+        <v>14.72</v>
       </c>
       <c r="I70" t="n">
-        <v>0.79</v>
+        <v>1.17</v>
       </c>
       <c r="J70" t="n">
-        <v>3.51</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="71">
@@ -2928,11 +2944,11 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>61.2</v>
+        <v>60</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.82pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.45pp)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2940,22 +2956,22 @@
         <v>42</v>
       </c>
       <c r="G71" t="n">
-        <v>52.4</v>
+        <v>42.9</v>
       </c>
       <c r="H71" t="n">
-        <v>7.23</v>
+        <v>2.43</v>
       </c>
       <c r="I71" t="n">
-        <v>2.41</v>
+        <v>-2.02</v>
       </c>
       <c r="J71" t="n">
-        <v>4.62</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2964,34 +2980,34 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.43pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.92pp)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G72" t="n">
-        <v>56.4</v>
+        <v>40.5</v>
       </c>
       <c r="H72" t="n">
-        <v>5.12</v>
+        <v>2.36</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.56</v>
       </c>
       <c r="J72" t="n">
-        <v>3.84</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3000,34 +3016,30 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>61</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.33pp)</t>
-        </is>
-      </c>
+        <v>59.2</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G73" t="n">
-        <v>55.9</v>
+        <v>36.1</v>
       </c>
       <c r="H73" t="n">
-        <v>9.49</v>
+        <v>1.3</v>
       </c>
       <c r="I73" t="n">
-        <v>3.16</v>
+        <v>-1.6</v>
       </c>
       <c r="J73" t="n">
-        <v>5.92</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3036,34 +3048,34 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>61</v>
+        <v>59.1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.95pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.93pp)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G74" t="n">
-        <v>56.2</v>
+        <v>45.5</v>
       </c>
       <c r="H74" t="n">
-        <v>9.630000000000001</v>
+        <v>6.02</v>
       </c>
       <c r="I74" t="n">
-        <v>1.68</v>
+        <v>-1.91</v>
       </c>
       <c r="J74" t="n">
-        <v>4.05</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3072,28 +3084,32 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>60.8</v>
+        <v>59</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.34pp)</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.07pp)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F75" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G75" t="n">
-        <v>58.5</v>
+        <v>45.5</v>
       </c>
       <c r="H75" t="n">
-        <v>6.29</v>
+        <v>9.98</v>
       </c>
       <c r="I75" t="n">
-        <v>0.95</v>
+        <v>-0.09</v>
       </c>
       <c r="J75" t="n">
-        <v>4.73</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="76">
@@ -3108,34 +3124,38 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>60.7</v>
+        <v>58.7</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.37pp)</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.75pp)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F76" t="n">
         <v>42</v>
       </c>
       <c r="G76" t="n">
-        <v>57.1</v>
+        <v>40.5</v>
       </c>
       <c r="H76" t="n">
-        <v>5.11</v>
+        <v>1.56</v>
       </c>
       <c r="I76" t="n">
-        <v>0.74</v>
+        <v>-2.19</v>
       </c>
       <c r="J76" t="n">
-        <v>4.56</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3144,34 +3164,34 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>60.5</v>
+        <v>57.4</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.18pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.34pp)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G77" t="n">
-        <v>60.6</v>
+        <v>45.7</v>
       </c>
       <c r="H77" t="n">
-        <v>6.2</v>
+        <v>3.03</v>
       </c>
       <c r="I77" t="n">
-        <v>2.02</v>
+        <v>-2.31</v>
       </c>
       <c r="J77" t="n">
-        <v>7.79</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3180,11 +3200,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>60.3</v>
+        <v>57.2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.73pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.88pp)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3193,25 +3213,25 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G78" t="n">
-        <v>56.7</v>
+        <v>50</v>
       </c>
       <c r="H78" t="n">
-        <v>14.17</v>
+        <v>15.06</v>
       </c>
       <c r="I78" t="n">
-        <v>4.44</v>
+        <v>-0.82</v>
       </c>
       <c r="J78" t="n">
-        <v>6.02</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3220,34 +3240,38 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>60.2</v>
+        <v>56.9</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.60pp)</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.12pp)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F79" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G79" t="n">
-        <v>54.5</v>
+        <v>42.4</v>
       </c>
       <c r="H79" t="n">
-        <v>7.98</v>
+        <v>6.28</v>
       </c>
       <c r="I79" t="n">
-        <v>1.38</v>
+        <v>-1.84</v>
       </c>
       <c r="J79" t="n">
-        <v>4.02</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3256,30 +3280,34 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
+        <v>56.2</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.71pp)</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G80" t="n">
-        <v>55.6</v>
+        <v>46.7</v>
       </c>
       <c r="H80" t="n">
-        <v>3.63</v>
+        <v>9.44</v>
       </c>
       <c r="I80" t="n">
-        <v>1.32</v>
+        <v>-1.27</v>
       </c>
       <c r="J80" t="n">
-        <v>5.66</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3288,66 +3316,70 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>60</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
+        <v>56.1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.04pp)</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G81" t="n">
-        <v>54.3</v>
+        <v>38.2</v>
       </c>
       <c r="H81" t="n">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>-1.72</v>
       </c>
       <c r="J81" t="n">
-        <v>4.68</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BANKNIFTY</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>59.5</v>
+        <v>55.4</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.04pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.83pp)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G82" t="n">
-        <v>53.2</v>
+        <v>46.4</v>
       </c>
       <c r="H82" t="n">
-        <v>3.55</v>
+        <v>4.87</v>
       </c>
       <c r="I82" t="n">
-        <v>0.51</v>
+        <v>-1.96</v>
       </c>
       <c r="J82" t="n">
-        <v>2.15</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3356,34 +3388,38 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>59.5</v>
+        <v>55.3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.18pp)</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 93.82pp)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F83" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G83" t="n">
-        <v>55.6</v>
+        <v>47.8</v>
       </c>
       <c r="H83" t="n">
-        <v>9.34</v>
+        <v>93.27</v>
       </c>
       <c r="I83" t="n">
-        <v>2.16</v>
+        <v>-0.55</v>
       </c>
       <c r="J83" t="n">
-        <v>4.83</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3392,38 +3428,34 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>59.3</v>
+        <v>55.3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.63pp)</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.19pp)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G84" t="n">
-        <v>57.5</v>
+        <v>41.7</v>
       </c>
       <c r="H84" t="n">
-        <v>11.49</v>
+        <v>0.47</v>
       </c>
       <c r="I84" t="n">
-        <v>2.86</v>
+        <v>-2.72</v>
       </c>
       <c r="J84" t="n">
-        <v>5.43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3432,34 +3464,34 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>59.2</v>
+        <v>55.2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 20.57pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.45pp)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G85" t="n">
-        <v>65</v>
+        <v>33.3</v>
       </c>
       <c r="H85" t="n">
-        <v>25.6</v>
+        <v>1.53</v>
       </c>
       <c r="I85" t="n">
-        <v>5.03</v>
+        <v>-1.92</v>
       </c>
       <c r="J85" t="n">
-        <v>9.68</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3468,34 +3500,38 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>59.1</v>
+        <v>54.3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.76pp)</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 22.35pp)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F86" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G86" t="n">
-        <v>52.5</v>
+        <v>48.3</v>
       </c>
       <c r="H86" t="n">
-        <v>4.69</v>
+        <v>21.49</v>
       </c>
       <c r="I86" t="n">
-        <v>0.93</v>
+        <v>-0.86</v>
       </c>
       <c r="J86" t="n">
-        <v>3.76</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3504,34 +3540,38 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>59</v>
+        <v>54.3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.32pp)</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.84pp)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F87" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G87" t="n">
-        <v>54.1</v>
+        <v>46.4</v>
       </c>
       <c r="H87" t="n">
-        <v>5.42</v>
+        <v>5.59</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>-1.25</v>
       </c>
       <c r="J87" t="n">
-        <v>4.6</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3540,34 +3580,30 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>59</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.39pp)</t>
-        </is>
-      </c>
+        <v>54.1</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G88" t="n">
-        <v>55.3</v>
+        <v>33.3</v>
       </c>
       <c r="H88" t="n">
-        <v>5.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>0.76</v>
+        <v>-2.34</v>
       </c>
       <c r="J88" t="n">
-        <v>4.23</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3576,30 +3612,34 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.54pp)</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G89" t="n">
-        <v>53.5</v>
+        <v>32.4</v>
       </c>
       <c r="H89" t="n">
-        <v>2.95</v>
+        <v>1.58</v>
       </c>
       <c r="I89" t="n">
-        <v>0.24</v>
+        <v>-1.96</v>
       </c>
       <c r="J89" t="n">
-        <v>3.49</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ICICILIFE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3608,34 +3648,34 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>58.3</v>
+        <v>53.2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.20pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.25pp)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G90" t="n">
-        <v>51.4</v>
+        <v>41.4</v>
       </c>
       <c r="H90" t="n">
-        <v>5.14</v>
+        <v>3.48</v>
       </c>
       <c r="I90" t="n">
-        <v>1.94</v>
+        <v>-1.77</v>
       </c>
       <c r="J90" t="n">
-        <v>5.05</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3644,38 +3684,34 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>57.5</v>
+        <v>52.9</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.58pp)</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.85pp)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G91" t="n">
-        <v>63.6</v>
+        <v>41.4</v>
       </c>
       <c r="H91" t="n">
-        <v>14.51</v>
+        <v>3.23</v>
       </c>
       <c r="I91" t="n">
-        <v>2.93</v>
+        <v>-2.62</v>
       </c>
       <c r="J91" t="n">
-        <v>6.89</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3684,34 +3720,38 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>57.3</v>
+        <v>52.9</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 16.37pp)</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.59pp)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G92" t="n">
-        <v>60</v>
+        <v>46.5</v>
       </c>
       <c r="H92" t="n">
-        <v>20.3</v>
+        <v>3.81</v>
       </c>
       <c r="I92" t="n">
-        <v>3.93</v>
+        <v>-2.78</v>
       </c>
       <c r="J92" t="n">
-        <v>6.86</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3720,30 +3760,34 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+        <v>52.8</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.90pp)</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G93" t="n">
-        <v>51.4</v>
+        <v>43.9</v>
       </c>
       <c r="H93" t="n">
-        <v>2.95</v>
+        <v>4.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.72</v>
+        <v>-1.85</v>
       </c>
       <c r="J93" t="n">
-        <v>4.06</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3752,34 +3796,38 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>56.6</v>
+        <v>52.8</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.78pp)</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.52pp)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F94" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G94" t="n">
-        <v>54.5</v>
+        <v>44.7</v>
       </c>
       <c r="H94" t="n">
-        <v>9.07</v>
+        <v>6.96</v>
       </c>
       <c r="I94" t="n">
-        <v>1.29</v>
+        <v>-1.56</v>
       </c>
       <c r="J94" t="n">
-        <v>4.09</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3788,34 +3836,34 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>55.4</v>
+        <v>52.7</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.82pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.14pp)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G95" t="n">
-        <v>52.9</v>
+        <v>40</v>
       </c>
       <c r="H95" t="n">
-        <v>6.99</v>
+        <v>1.44</v>
       </c>
       <c r="I95" t="n">
-        <v>1.17</v>
+        <v>-2.7</v>
       </c>
       <c r="J95" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3824,34 +3872,30 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 34.66pp)</t>
-        </is>
-      </c>
+        <v>52.5</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G96" t="n">
-        <v>59.3</v>
+        <v>33.3</v>
       </c>
       <c r="H96" t="n">
-        <v>39.43</v>
+        <v>0.3</v>
       </c>
       <c r="I96" t="n">
-        <v>4.77</v>
+        <v>-2.48</v>
       </c>
       <c r="J96" t="n">
-        <v>8.539999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3860,34 +3904,38 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>54.1</v>
+        <v>52.4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.07pp)</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.20pp)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F97" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G97" t="n">
-        <v>52.5</v>
+        <v>36.4</v>
       </c>
       <c r="H97" t="n">
-        <v>4.77</v>
+        <v>0.88</v>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>-2.32</v>
       </c>
       <c r="J97" t="n">
-        <v>6.46</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3896,34 +3944,34 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.85pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.07pp)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G98" t="n">
-        <v>55.9</v>
+        <v>35</v>
       </c>
       <c r="H98" t="n">
-        <v>9.81</v>
+        <v>1.57</v>
       </c>
       <c r="I98" t="n">
-        <v>2.96</v>
+        <v>-2.5</v>
       </c>
       <c r="J98" t="n">
-        <v>7.93</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3932,34 +3980,34 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>53.4</v>
+        <v>51.9</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.35pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.64pp)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G99" t="n">
-        <v>52.9</v>
+        <v>47.2</v>
       </c>
       <c r="H99" t="n">
-        <v>4.59</v>
+        <v>5.4</v>
       </c>
       <c r="I99" t="n">
-        <v>0.24</v>
+        <v>-2.24</v>
       </c>
       <c r="J99" t="n">
-        <v>3.74</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3968,38 +4016,30 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.77pp)</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+        <v>51.8</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G100" t="n">
-        <v>53.6</v>
+        <v>31.6</v>
       </c>
       <c r="H100" t="n">
-        <v>9.43</v>
+        <v>1.07</v>
       </c>
       <c r="I100" t="n">
-        <v>2.66</v>
+        <v>-1.54</v>
       </c>
       <c r="J100" t="n">
-        <v>6.2</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4008,34 +4048,34 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>52.7</v>
+        <v>51.3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.14pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.25pp)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G101" t="n">
-        <v>55.8</v>
+        <v>44.1</v>
       </c>
       <c r="H101" t="n">
-        <v>5.75</v>
+        <v>5.73</v>
       </c>
       <c r="I101" t="n">
-        <v>0.61</v>
+        <v>-1.52</v>
       </c>
       <c r="J101" t="n">
-        <v>5.1</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4044,34 +4084,34 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>52.5</v>
+        <v>51.2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 13.61pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.13pp)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G102" t="n">
-        <v>56.1</v>
+        <v>43.6</v>
       </c>
       <c r="H102" t="n">
-        <v>16.56</v>
+        <v>3.17</v>
       </c>
       <c r="I102" t="n">
-        <v>2.95</v>
+        <v>-1.96</v>
       </c>
       <c r="J102" t="n">
-        <v>6.05</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4080,34 +4120,38 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>52</v>
+        <v>51.2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.81pp)</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.25pp)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F103" t="n">
         <v>34</v>
       </c>
       <c r="G103" t="n">
-        <v>52.9</v>
+        <v>41.2</v>
       </c>
       <c r="H103" t="n">
-        <v>8.83</v>
+        <v>3.71</v>
       </c>
       <c r="I103" t="n">
-        <v>2.02</v>
+        <v>-2.54</v>
       </c>
       <c r="J103" t="n">
-        <v>5.62</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4116,34 +4160,38 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>51.8</v>
+        <v>50.8</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.04pp)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.83pp)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F104" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G104" t="n">
-        <v>52.8</v>
+        <v>41.5</v>
       </c>
       <c r="H104" t="n">
-        <v>7.66</v>
+        <v>3.92</v>
       </c>
       <c r="I104" t="n">
-        <v>1.62</v>
+        <v>-1.91</v>
       </c>
       <c r="J104" t="n">
-        <v>5.42</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4156,30 +4204,34 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 18.16pp)</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.87pp)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F105" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G105" t="n">
-        <v>54.5</v>
+        <v>40.5</v>
       </c>
       <c r="H105" t="n">
-        <v>21.54</v>
+        <v>3.15</v>
       </c>
       <c r="I105" t="n">
-        <v>3.38</v>
+        <v>-2.72</v>
       </c>
       <c r="J105" t="n">
-        <v>6.35</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4188,34 +4240,34 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>49.9</v>
+        <v>50.4</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.73pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.92pp)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G106" t="n">
-        <v>56.4</v>
+        <v>43.8</v>
       </c>
       <c r="H106" t="n">
-        <v>7.39</v>
+        <v>3.7</v>
       </c>
       <c r="I106" t="n">
-        <v>0.66</v>
+        <v>-2.22</v>
       </c>
       <c r="J106" t="n">
-        <v>5.3</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4224,34 +4276,34 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>49.3</v>
+        <v>50.2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.78pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.47pp)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G107" t="n">
-        <v>58.1</v>
+        <v>40.9</v>
       </c>
       <c r="H107" t="n">
-        <v>9.369999999999999</v>
+        <v>3.88</v>
       </c>
       <c r="I107" t="n">
-        <v>0.59</v>
+        <v>-2.59</v>
       </c>
       <c r="J107" t="n">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4260,34 +4312,38 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.73pp)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.11pp)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F108" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G108" t="n">
-        <v>52.5</v>
+        <v>47.2</v>
       </c>
       <c r="H108" t="n">
-        <v>6.01</v>
+        <v>7.68</v>
       </c>
       <c r="I108" t="n">
-        <v>0.28</v>
+        <v>-1.43</v>
       </c>
       <c r="J108" t="n">
-        <v>4.14</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4296,34 +4352,34 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>48.7</v>
+        <v>49.8</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.50pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.46pp)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G109" t="n">
-        <v>51.4</v>
+        <v>37</v>
       </c>
       <c r="H109" t="n">
-        <v>5.08</v>
+        <v>0.66</v>
       </c>
       <c r="I109" t="n">
-        <v>0.58</v>
+        <v>-2.8</v>
       </c>
       <c r="J109" t="n">
-        <v>4.54</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4332,34 +4388,34 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>48.3</v>
+        <v>49.8</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.30pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.14pp)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G110" t="n">
-        <v>52.2</v>
+        <v>38.9</v>
       </c>
       <c r="H110" t="n">
-        <v>3.47</v>
+        <v>3.68</v>
       </c>
       <c r="I110" t="n">
-        <v>0.17</v>
+        <v>-1.46</v>
       </c>
       <c r="J110" t="n">
-        <v>4.65</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4368,34 +4424,34 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>48.1</v>
+        <v>49.4</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.42pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.82pp)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G111" t="n">
-        <v>52.5</v>
+        <v>42.9</v>
       </c>
       <c r="H111" t="n">
-        <v>3.62</v>
+        <v>7.88</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2</v>
+        <v>-1.94</v>
       </c>
       <c r="J111" t="n">
-        <v>5.01</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4404,38 +4460,34 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>48</v>
+        <v>49.4</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 23.18pp)</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.06pp)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G112" t="n">
-        <v>55.2</v>
+        <v>40.5</v>
       </c>
       <c r="H112" t="n">
-        <v>26.63</v>
+        <v>1.68</v>
       </c>
       <c r="I112" t="n">
-        <v>3.45</v>
+        <v>-2.38</v>
       </c>
       <c r="J112" t="n">
-        <v>7.5</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4444,34 +4496,34 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>47.6</v>
+        <v>49</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.40pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.23pp)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G113" t="n">
-        <v>51.3</v>
+        <v>41.9</v>
       </c>
       <c r="H113" t="n">
-        <v>3.96</v>
+        <v>1.91</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.32</v>
       </c>
       <c r="J113" t="n">
-        <v>4.99</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4480,34 +4532,34 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.44pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.77pp)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G114" t="n">
-        <v>52.3</v>
+        <v>41.9</v>
       </c>
       <c r="H114" t="n">
-        <v>4.8</v>
+        <v>4.37</v>
       </c>
       <c r="I114" t="n">
-        <v>1.36</v>
+        <v>-2.4</v>
       </c>
       <c r="J114" t="n">
-        <v>7.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4516,34 +4568,34 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>47.3</v>
+        <v>48.8</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.23pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.78pp)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G115" t="n">
-        <v>52.4</v>
+        <v>38.2</v>
       </c>
       <c r="H115" t="n">
-        <v>5.35</v>
+        <v>5.53</v>
       </c>
       <c r="I115" t="n">
-        <v>1.12</v>
+        <v>-1.25</v>
       </c>
       <c r="J115" t="n">
-        <v>6.38</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4552,34 +4604,34 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>47.1</v>
+        <v>48.1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.24pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 33.49pp)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6</v>
+        <v>48.1</v>
       </c>
       <c r="H116" t="n">
-        <v>11.42</v>
+        <v>32.17</v>
       </c>
       <c r="I116" t="n">
-        <v>0.18</v>
+        <v>-1.32</v>
       </c>
       <c r="J116" t="n">
-        <v>4.34</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4588,38 +4640,34 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.97pp)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.69pp)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G117" t="n">
-        <v>53.7</v>
+        <v>43.8</v>
       </c>
       <c r="H117" t="n">
-        <v>7.57</v>
+        <v>3.91</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>-2.78</v>
       </c>
       <c r="J117" t="n">
-        <v>4.83</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4628,34 +4676,34 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.78pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.00pp)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G118" t="n">
-        <v>54.3</v>
+        <v>45.2</v>
       </c>
       <c r="H118" t="n">
-        <v>7.3</v>
+        <v>2.99</v>
       </c>
       <c r="I118" t="n">
-        <v>0.52</v>
+        <v>-3.01</v>
       </c>
       <c r="J118" t="n">
-        <v>4.97</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4664,34 +4712,38 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>46.3</v>
+        <v>47.4</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.24pp)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.27pp)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F119" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G119" t="n">
-        <v>55.6</v>
+        <v>43.8</v>
       </c>
       <c r="H119" t="n">
-        <v>10.06</v>
+        <v>6.91</v>
       </c>
       <c r="I119" t="n">
-        <v>1.82</v>
+        <v>-2.36</v>
       </c>
       <c r="J119" t="n">
-        <v>7.44</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4704,30 +4756,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.45pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.69pp)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G120" t="n">
-        <v>52.8</v>
+        <v>44.1</v>
       </c>
       <c r="H120" t="n">
-        <v>4.74</v>
+        <v>5.75</v>
       </c>
       <c r="I120" t="n">
-        <v>0.29</v>
+        <v>-1.94</v>
       </c>
       <c r="J120" t="n">
-        <v>5.16</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4736,34 +4788,34 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.52pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.54pp)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G121" t="n">
-        <v>54.1</v>
+        <v>35</v>
       </c>
       <c r="H121" t="n">
-        <v>8.24</v>
+        <v>1.68</v>
       </c>
       <c r="I121" t="n">
-        <v>0.72</v>
+        <v>-2.86</v>
       </c>
       <c r="J121" t="n">
-        <v>5.17</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4772,11 +4824,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.83pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.02pp)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4784,22 +4836,22 @@
         <v>39</v>
       </c>
       <c r="G122" t="n">
-        <v>53.8</v>
+        <v>38.5</v>
       </c>
       <c r="H122" t="n">
-        <v>6.6</v>
+        <v>1.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.77</v>
+        <v>-2.94</v>
       </c>
       <c r="J122" t="n">
-        <v>5.98</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4808,34 +4860,38 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>45.6</v>
+        <v>43.9</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.02pp)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.89pp)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F123" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G123" t="n">
-        <v>52</v>
+        <v>42.4</v>
       </c>
       <c r="H123" t="n">
-        <v>4.21</v>
+        <v>2.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.19</v>
+        <v>-2.65</v>
       </c>
       <c r="J123" t="n">
-        <v>4.84</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4844,11 +4900,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>45.3</v>
+        <v>43.2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.69pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.08pp)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4856,22 +4912,22 @@
         <v>39</v>
       </c>
       <c r="G124" t="n">
-        <v>53.8</v>
+        <v>38.5</v>
       </c>
       <c r="H124" t="n">
-        <v>8.880000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="I124" t="n">
-        <v>1.19</v>
+        <v>-2.69</v>
       </c>
       <c r="J124" t="n">
-        <v>6.01</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4880,34 +4936,34 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>44.6</v>
+        <v>43.1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 19.52pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 19.50pp)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G125" t="n">
-        <v>52.4</v>
+        <v>45</v>
       </c>
       <c r="H125" t="n">
-        <v>24.08</v>
+        <v>18.01</v>
       </c>
       <c r="I125" t="n">
-        <v>4.56</v>
+        <v>-1.49</v>
       </c>
       <c r="J125" t="n">
-        <v>8.94</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4916,34 +4972,34 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 12.75pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.70pp)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G126" t="n">
-        <v>57.9</v>
+        <v>35</v>
       </c>
       <c r="H126" t="n">
-        <v>13.97</v>
+        <v>2.94</v>
       </c>
       <c r="I126" t="n">
-        <v>1.22</v>
+        <v>-2.76</v>
       </c>
       <c r="J126" t="n">
-        <v>6.99</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4952,34 +5008,34 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>43.8</v>
+        <v>42.9</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.16pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.58pp)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G127" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="H127" t="n">
-        <v>5.56</v>
+        <v>0.31</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>-3.27</v>
       </c>
       <c r="J127" t="n">
-        <v>4.67</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4988,34 +5044,34 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>43.8</v>
+        <v>42.7</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.51pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.25pp)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G128" t="n">
-        <v>52.8</v>
+        <v>37</v>
       </c>
       <c r="H128" t="n">
-        <v>7.32</v>
+        <v>-0.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.43</v>
       </c>
       <c r="J128" t="n">
-        <v>5.82</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5024,34 +5080,34 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>43.4</v>
+        <v>42.5</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.05pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.69pp)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G129" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="H129" t="n">
-        <v>2.93</v>
+        <v>0.63</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.12</v>
+        <v>-4.06</v>
       </c>
       <c r="J129" t="n">
-        <v>4.53</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5060,34 +5116,34 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>43.4</v>
+        <v>42.5</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.10pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.64pp)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G130" t="n">
-        <v>52.9</v>
+        <v>41</v>
       </c>
       <c r="H130" t="n">
-        <v>6.27</v>
+        <v>5.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.17</v>
+        <v>-2.6</v>
       </c>
       <c r="J130" t="n">
-        <v>4.93</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5096,34 +5152,30 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.56pp)</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G131" t="n">
-        <v>51.3</v>
+        <v>32.4</v>
       </c>
       <c r="H131" t="n">
-        <v>7.02</v>
+        <v>-0.88</v>
       </c>
       <c r="I131" t="n">
-        <v>0.46</v>
+        <v>-3.33</v>
       </c>
       <c r="J131" t="n">
-        <v>4.62</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5132,38 +5184,34 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>43.1</v>
+        <v>41.7</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.60pp)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.37pp)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G132" t="n">
-        <v>53.5</v>
+        <v>36.1</v>
       </c>
       <c r="H132" t="n">
-        <v>14.15</v>
+        <v>0.87</v>
       </c>
       <c r="I132" t="n">
-        <v>2.55</v>
+        <v>-3.5</v>
       </c>
       <c r="J132" t="n">
-        <v>8.210000000000001</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5172,38 +5220,34 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.44pp)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.38pp)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G133" t="n">
-        <v>56.2</v>
+        <v>36.4</v>
       </c>
       <c r="H133" t="n">
-        <v>9.85</v>
+        <v>3.65</v>
       </c>
       <c r="I133" t="n">
-        <v>0.41</v>
+        <v>-2.73</v>
       </c>
       <c r="J133" t="n">
-        <v>5.6</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5212,34 +5256,38 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>41.4</v>
+        <v>41</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.01pp)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.09pp)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F134" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G134" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H134" t="n">
-        <v>3.75</v>
+        <v>6.27</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.26</v>
+        <v>-2.82</v>
       </c>
       <c r="J134" t="n">
-        <v>4.68</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5248,34 +5296,34 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>41.3</v>
+        <v>40.7</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.81pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.72pp)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G135" t="n">
-        <v>53.8</v>
+        <v>36.8</v>
       </c>
       <c r="H135" t="n">
-        <v>8.01</v>
+        <v>10.6</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2</v>
+        <v>-1.12</v>
       </c>
       <c r="J135" t="n">
-        <v>5.11</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5284,34 +5332,34 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>41.2</v>
+        <v>40.4</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.92pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.32pp)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G136" t="n">
-        <v>50</v>
+        <v>43.2</v>
       </c>
       <c r="H136" t="n">
-        <v>3.95</v>
+        <v>6.17</v>
       </c>
       <c r="I136" t="n">
-        <v>0.03</v>
+        <v>-2.15</v>
       </c>
       <c r="J136" t="n">
-        <v>5.08</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5320,34 +5368,34 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>41</v>
+        <v>40.3</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.04pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.13pp)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G137" t="n">
-        <v>52.4</v>
+        <v>37</v>
       </c>
       <c r="H137" t="n">
-        <v>9.41</v>
+        <v>0.85</v>
       </c>
       <c r="I137" t="n">
-        <v>1.37</v>
+        <v>-3.28</v>
       </c>
       <c r="J137" t="n">
-        <v>6.64</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5356,34 +5404,34 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>41</v>
+        <v>39.3</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.25pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.14pp)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G138" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H138" t="n">
-        <v>12.83</v>
+        <v>-0.13</v>
       </c>
       <c r="I138" t="n">
-        <v>1.58</v>
+        <v>-3.27</v>
       </c>
       <c r="J138" t="n">
-        <v>7.61</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5392,34 +5440,38 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.14pp)</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.69pp)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F139" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G139" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H139" t="n">
-        <v>3.52</v>
+        <v>2.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.62</v>
+        <v>-2.82</v>
       </c>
       <c r="J139" t="n">
-        <v>4.58</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5428,34 +5480,38 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>40.4</v>
+        <v>38.3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.50pp)</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.12pp)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F140" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G140" t="n">
-        <v>50</v>
+        <v>43.2</v>
       </c>
       <c r="H140" t="n">
-        <v>7.36</v>
+        <v>0.04</v>
       </c>
       <c r="I140" t="n">
-        <v>0.86</v>
+        <v>-4.08</v>
       </c>
       <c r="J140" t="n">
-        <v>5.68</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5464,34 +5520,34 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.21pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.51pp)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G141" t="n">
-        <v>51.2</v>
+        <v>36.8</v>
       </c>
       <c r="H141" t="n">
-        <v>6.37</v>
+        <v>0.45</v>
       </c>
       <c r="I141" t="n">
-        <v>0.16</v>
+        <v>-4.06</v>
       </c>
       <c r="J141" t="n">
-        <v>4.78</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5500,30 +5556,34 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="D142" t="inlineStr"/>
+        <v>37.9</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.51pp)</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G142" t="n">
-        <v>45.9</v>
+        <v>34.1</v>
       </c>
       <c r="H142" t="n">
-        <v>2.53</v>
+        <v>1.1</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.09</v>
+        <v>-3.41</v>
       </c>
       <c r="J142" t="n">
-        <v>5.44</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5532,34 +5592,38 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>38.6</v>
+        <v>37.8</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 14.08pp)</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.66pp)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F143" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G143" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="H143" t="n">
-        <v>17.22</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I143" t="n">
-        <v>3.14</v>
+        <v>-2.7</v>
       </c>
       <c r="J143" t="n">
-        <v>8.800000000000001</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5568,34 +5632,34 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.93pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.21pp)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G144" t="n">
-        <v>52.8</v>
+        <v>40.5</v>
       </c>
       <c r="H144" t="n">
-        <v>12.63</v>
+        <v>4.71</v>
       </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="J144" t="n">
-        <v>8.720000000000001</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5604,34 +5668,38 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>37.7</v>
+        <v>36.7</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.26pp)</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.97pp)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F145" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G145" t="n">
-        <v>48.7</v>
+        <v>44.1</v>
       </c>
       <c r="H145" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.48</v>
+        <v>-3.37</v>
       </c>
       <c r="J145" t="n">
-        <v>4.23</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5640,11 +5708,11 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>37.7</v>
+        <v>36.7</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.31pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.66pp)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5652,22 +5720,22 @@
         <v>39</v>
       </c>
       <c r="G146" t="n">
-        <v>51.3</v>
+        <v>33.3</v>
       </c>
       <c r="H146" t="n">
-        <v>8.16</v>
+        <v>-0.05</v>
       </c>
       <c r="I146" t="n">
-        <v>0.85</v>
+        <v>-3.71</v>
       </c>
       <c r="J146" t="n">
-        <v>6.08</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5676,34 +5744,38 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.15pp)</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.05pp)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F147" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G147" t="n">
-        <v>45</v>
+        <v>35.9</v>
       </c>
       <c r="H147" t="n">
-        <v>4.29</v>
+        <v>2.47</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.86</v>
+        <v>-3.58</v>
       </c>
       <c r="J147" t="n">
-        <v>3.76</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5712,34 +5784,34 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>36.6</v>
+        <v>36.2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.31pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.01pp)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G148" t="n">
-        <v>52.4</v>
+        <v>35.7</v>
       </c>
       <c r="H148" t="n">
-        <v>7.88</v>
+        <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.57</v>
+        <v>-3.77</v>
       </c>
       <c r="J148" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5748,34 +5820,38 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.02pp)</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.58pp)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F149" t="n">
         <v>39</v>
       </c>
       <c r="G149" t="n">
-        <v>51.3</v>
+        <v>38.5</v>
       </c>
       <c r="H149" t="n">
-        <v>5.08</v>
+        <v>1.42</v>
       </c>
       <c r="I149" t="n">
-        <v>0.06</v>
+        <v>-3.16</v>
       </c>
       <c r="J149" t="n">
-        <v>5.93</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5784,34 +5860,38 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.05pp)</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 13.99pp)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F150" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G150" t="n">
-        <v>44.2</v>
+        <v>39.3</v>
       </c>
       <c r="H150" t="n">
-        <v>2.76</v>
+        <v>11.44</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.29</v>
+        <v>-2.55</v>
       </c>
       <c r="J150" t="n">
-        <v>5.4</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5820,38 +5900,34 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>35.2</v>
+        <v>35.6</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 99.42pp)</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.43pp)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G151" t="n">
-        <v>52.2</v>
+        <v>37.1</v>
       </c>
       <c r="H151" t="n">
-        <v>101.17</v>
+        <v>5.6</v>
       </c>
       <c r="I151" t="n">
-        <v>1.75</v>
+        <v>-2.83</v>
       </c>
       <c r="J151" t="n">
-        <v>7.17</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ICICILIFE</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5860,34 +5936,34 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>32.7</v>
+        <v>35.5</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.65pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.00pp)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G152" t="n">
-        <v>48.3</v>
+        <v>30.8</v>
       </c>
       <c r="H152" t="n">
-        <v>6.55</v>
+        <v>2.57</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1</v>
+        <v>-3.43</v>
       </c>
       <c r="J152" t="n">
-        <v>5.21</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5896,34 +5972,34 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>32.6</v>
+        <v>35.5</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.43pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.09pp)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G153" t="n">
-        <v>43.2</v>
+        <v>34.9</v>
       </c>
       <c r="H153" t="n">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="I153" t="n">
-        <v>-1.5</v>
+        <v>-2.81</v>
       </c>
       <c r="J153" t="n">
-        <v>4.31</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5932,34 +6008,34 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>32</v>
+        <v>35.2</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.62pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.95pp)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G154" t="n">
-        <v>48.1</v>
+        <v>29.5</v>
       </c>
       <c r="H154" t="n">
-        <v>6.04</v>
+        <v>-0.44</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.58</v>
+        <v>-4.39</v>
       </c>
       <c r="J154" t="n">
-        <v>4.85</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5968,34 +6044,34 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>31.8</v>
+        <v>34.9</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.51pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.09pp)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G155" t="n">
-        <v>48.5</v>
+        <v>37.2</v>
       </c>
       <c r="H155" t="n">
-        <v>8.289999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.22</v>
+        <v>-3.55</v>
       </c>
       <c r="J155" t="n">
-        <v>4.69</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6004,34 +6080,34 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>31.5</v>
+        <v>34.3</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.82pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.35pp)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G156" t="n">
-        <v>51.4</v>
+        <v>34.9</v>
       </c>
       <c r="H156" t="n">
-        <v>11.2</v>
+        <v>-0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>0.38</v>
+        <v>-4.24</v>
       </c>
       <c r="J156" t="n">
-        <v>5.74</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6040,34 +6116,34 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>31.3</v>
+        <v>33.9</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.92pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.50pp)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G157" t="n">
-        <v>52.5</v>
+        <v>35.9</v>
       </c>
       <c r="H157" t="n">
-        <v>8.17</v>
+        <v>4.07</v>
       </c>
       <c r="I157" t="n">
-        <v>0.25</v>
+        <v>-3.43</v>
       </c>
       <c r="J157" t="n">
-        <v>7.46</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6076,34 +6152,34 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>30.8</v>
+        <v>33.5</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 3.40pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.04pp)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G158" t="n">
-        <v>46.4</v>
+        <v>42.4</v>
       </c>
       <c r="H158" t="n">
-        <v>2.34</v>
+        <v>3.44</v>
       </c>
       <c r="I158" t="n">
-        <v>-1.06</v>
+        <v>-3.6</v>
       </c>
       <c r="J158" t="n">
-        <v>5.76</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6112,34 +6188,34 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.34pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.74pp)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G159" t="n">
-        <v>46.7</v>
+        <v>38.5</v>
       </c>
       <c r="H159" t="n">
-        <v>6.96</v>
+        <v>3.4</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.38</v>
+        <v>-3.34</v>
       </c>
       <c r="J159" t="n">
-        <v>4.89</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6148,11 +6224,11 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>30.2</v>
+        <v>32.1</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 14.04pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 12.94pp)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6161,25 +6237,25 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G160" t="n">
-        <v>51.6</v>
+        <v>41.2</v>
       </c>
       <c r="H160" t="n">
-        <v>15.12</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>1.08</v>
+        <v>-3.48</v>
       </c>
       <c r="J160" t="n">
-        <v>8.67</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6188,34 +6264,34 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>29.5</v>
+        <v>31.9</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.62pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 14.30pp)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G161" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="H161" t="n">
-        <v>3.99</v>
+        <v>11.01</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.63</v>
+        <v>-3.29</v>
       </c>
       <c r="J161" t="n">
-        <v>5.3</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6224,34 +6300,34 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>29.5</v>
+        <v>31.5</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.58pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.63pp)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G162" t="n">
-        <v>48.4</v>
+        <v>35.9</v>
       </c>
       <c r="H162" t="n">
-        <v>5.58</v>
+        <v>0.97</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>-3.66</v>
       </c>
       <c r="J162" t="n">
-        <v>6.89</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6260,34 +6336,38 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.16pp)</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.54pp)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F163" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G163" t="n">
-        <v>47.7</v>
+        <v>35.5</v>
       </c>
       <c r="H163" t="n">
-        <v>3.81</v>
+        <v>4.64</v>
       </c>
       <c r="I163" t="n">
-        <v>-1.35</v>
+        <v>-2.9</v>
       </c>
       <c r="J163" t="n">
-        <v>5.26</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6296,34 +6376,34 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>28.7</v>
+        <v>29.8</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.92pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.67pp)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G164" t="n">
-        <v>45.7</v>
+        <v>37.5</v>
       </c>
       <c r="H164" t="n">
-        <v>4.02</v>
+        <v>1.07</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.9</v>
+        <v>-4.6</v>
       </c>
       <c r="J164" t="n">
-        <v>5.56</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6332,34 +6412,34 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>28.4</v>
+        <v>29.8</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.55pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.88pp)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G165" t="n">
-        <v>48.6</v>
+        <v>44.4</v>
       </c>
       <c r="H165" t="n">
-        <v>10.03</v>
+        <v>5.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.52</v>
+        <v>-4.12</v>
       </c>
       <c r="J165" t="n">
-        <v>4.83</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6368,11 +6448,11 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>27.5</v>
+        <v>29.6</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 14.81pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.70pp)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6381,25 +6461,25 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G166" t="n">
-        <v>52.4</v>
+        <v>41</v>
       </c>
       <c r="H166" t="n">
-        <v>15.37</v>
+        <v>-0.08</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5600000000000001</v>
+        <v>-4.78</v>
       </c>
       <c r="J166" t="n">
-        <v>7.54</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6408,11 +6488,11 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>27.3</v>
+        <v>29.2</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 33.74pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.36pp)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6421,25 +6501,25 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G167" t="n">
-        <v>50</v>
+        <v>34.5</v>
       </c>
       <c r="H167" t="n">
-        <v>34.34</v>
+        <v>0.49</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>-3.87</v>
       </c>
       <c r="J167" t="n">
-        <v>6.16</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6448,34 +6528,34 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>27.1</v>
+        <v>28.8</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.28pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.45pp)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G168" t="n">
-        <v>47.7</v>
+        <v>37.5</v>
       </c>
       <c r="H168" t="n">
-        <v>7.05</v>
+        <v>3.35</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.23</v>
+        <v>-3.1</v>
       </c>
       <c r="J168" t="n">
-        <v>5.81</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6484,28 +6564,32 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>27.1</v>
+        <v>28.7</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.10pp)</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 12.02pp)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F169" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G169" t="n">
-        <v>41.9</v>
+        <v>38.1</v>
       </c>
       <c r="H169" t="n">
-        <v>7.28</v>
+        <v>9.48</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.82</v>
+        <v>-2.54</v>
       </c>
       <c r="J169" t="n">
-        <v>4.48</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -6520,11 +6604,11 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>27</v>
+        <v>28.3</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.24pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.44pp)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6532,22 +6616,22 @@
         <v>18</v>
       </c>
       <c r="G170" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="H170" t="n">
-        <v>5.66</v>
+        <v>1.75</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.58</v>
+        <v>-3.69</v>
       </c>
       <c r="J170" t="n">
-        <v>5.6</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6556,38 +6640,34 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>25.8</v>
+        <v>28</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.37pp)</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.42pp)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G171" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="H171" t="n">
-        <v>8.15</v>
+        <v>3.76</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.22</v>
+        <v>-4.66</v>
       </c>
       <c r="J171" t="n">
-        <v>6.2</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6596,38 +6676,34 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.98pp)</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.65pp)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G172" t="n">
-        <v>46.4</v>
+        <v>30.4</v>
       </c>
       <c r="H172" t="n">
-        <v>15.65</v>
+        <v>1.7</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.33</v>
+        <v>-3.95</v>
       </c>
       <c r="J172" t="n">
-        <v>4.76</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6636,38 +6712,34 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>24.8</v>
+        <v>27</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 24.91pp)</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 16.94pp)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G173" t="n">
-        <v>54.1</v>
+        <v>46.7</v>
       </c>
       <c r="H173" t="n">
-        <v>25</v>
+        <v>12.67</v>
       </c>
       <c r="I173" t="n">
-        <v>0.09</v>
+        <v>-4.27</v>
       </c>
       <c r="J173" t="n">
-        <v>9.43</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6676,34 +6748,34 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>24.8</v>
+        <v>26.9</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.71pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.32pp)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G174" t="n">
-        <v>43.8</v>
+        <v>30</v>
       </c>
       <c r="H174" t="n">
-        <v>4.08</v>
+        <v>3.61</v>
       </c>
       <c r="I174" t="n">
-        <v>-1.63</v>
+        <v>-3.71</v>
       </c>
       <c r="J174" t="n">
-        <v>5.42</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6712,34 +6784,34 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.00pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.06pp)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G175" t="n">
-        <v>46.4</v>
+        <v>38.7</v>
       </c>
       <c r="H175" t="n">
-        <v>8.279999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.72</v>
+        <v>-3.92</v>
       </c>
       <c r="J175" t="n">
-        <v>5.3</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6748,34 +6820,34 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.69pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.17pp)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G176" t="n">
-        <v>44.2</v>
+        <v>32.5</v>
       </c>
       <c r="H176" t="n">
-        <v>6.35</v>
+        <v>-0.23</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.34</v>
+        <v>-4.4</v>
       </c>
       <c r="J176" t="n">
-        <v>5.04</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6784,34 +6856,38 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.92pp)</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.35pp)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G177" t="n">
-        <v>40</v>
+        <v>40.6</v>
       </c>
       <c r="H177" t="n">
-        <v>3.64</v>
+        <v>3.31</v>
       </c>
       <c r="I177" t="n">
-        <v>-2.28</v>
+        <v>-5.04</v>
       </c>
       <c r="J177" t="n">
-        <v>5.02</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6820,34 +6896,34 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>22.2</v>
+        <v>24.7</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.54pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.56pp)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G178" t="n">
-        <v>48.4</v>
+        <v>35</v>
       </c>
       <c r="H178" t="n">
-        <v>8.4</v>
+        <v>0.39</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.14</v>
+        <v>-5.17</v>
       </c>
       <c r="J178" t="n">
-        <v>7.05</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6856,38 +6932,34 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>22.1</v>
+        <v>23.7</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.41pp)</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.51pp)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G179" t="n">
-        <v>43.2</v>
+        <v>25.6</v>
       </c>
       <c r="H179" t="n">
-        <v>4.52</v>
+        <v>2.32</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.89</v>
+        <v>-4.19</v>
       </c>
       <c r="J179" t="n">
-        <v>6.79</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6896,34 +6968,34 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>22.1</v>
+        <v>23.7</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.74pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 4.90pp)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G180" t="n">
-        <v>45.5</v>
+        <v>30.4</v>
       </c>
       <c r="H180" t="n">
-        <v>10.67</v>
+        <v>-0.05</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.95</v>
       </c>
       <c r="J180" t="n">
-        <v>6.13</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6932,34 +7004,34 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>20.8</v>
+        <v>23.2</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.75pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.35pp)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6</v>
+        <v>34.3</v>
       </c>
       <c r="H181" t="n">
-        <v>15.61</v>
+        <v>4.31</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.14</v>
+        <v>-4.04</v>
       </c>
       <c r="J181" t="n">
-        <v>6.49</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6968,11 +7040,11 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>19.7</v>
+        <v>22.7</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.06pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 22.60pp)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6981,25 +7053,25 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G182" t="n">
-        <v>41.2</v>
+        <v>42.9</v>
       </c>
       <c r="H182" t="n">
-        <v>14.06</v>
+        <v>18.53</v>
       </c>
       <c r="I182" t="n">
-        <v>-1</v>
+        <v>-4.07</v>
       </c>
       <c r="J182" t="n">
-        <v>4.81</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7008,34 +7080,34 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>19.7</v>
+        <v>21.3</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.81pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.61pp)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G183" t="n">
-        <v>46.7</v>
+        <v>38.1</v>
       </c>
       <c r="H183" t="n">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="I183" t="n">
-        <v>-3.07</v>
+        <v>-4.48</v>
       </c>
       <c r="J183" t="n">
-        <v>6.76</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7044,34 +7116,38 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>19</v>
+        <v>21.1</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.92pp)</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.81pp)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G184" t="n">
-        <v>46.2</v>
+        <v>38.2</v>
       </c>
       <c r="H184" t="n">
-        <v>4.18</v>
+        <v>4.77</v>
       </c>
       <c r="I184" t="n">
-        <v>-1.74</v>
+        <v>-5.04</v>
       </c>
       <c r="J184" t="n">
-        <v>7.36</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7080,34 +7156,38 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>18.5</v>
+        <v>20.6</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.96pp)</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 24.59pp)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G185" t="n">
-        <v>43.5</v>
+        <v>45.9</v>
       </c>
       <c r="H185" t="n">
-        <v>4.92</v>
+        <v>17.95</v>
       </c>
       <c r="I185" t="n">
-        <v>-3.04</v>
+        <v>-6.64</v>
       </c>
       <c r="J185" t="n">
-        <v>5.35</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7116,34 +7196,38 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>18.3</v>
+        <v>20.5</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 27.48pp)</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 30.35pp)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G186" t="n">
-        <v>33.3</v>
+        <v>42.1</v>
       </c>
       <c r="H186" t="n">
-        <v>26.18</v>
+        <v>25.32</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.3</v>
+        <v>-5.03</v>
       </c>
       <c r="J186" t="n">
-        <v>4.43</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7152,34 +7236,34 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>18.3</v>
+        <v>20.4</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.98pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.75pp)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G187" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="H187" t="n">
-        <v>6.78</v>
+        <v>7.67</v>
       </c>
       <c r="I187" t="n">
-        <v>-1.2</v>
+        <v>-4.08</v>
       </c>
       <c r="J187" t="n">
-        <v>5.84</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7188,34 +7272,38 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>17.1</v>
+        <v>20.3</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 8.22pp)</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.83pp)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F188" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G188" t="n">
-        <v>45.5</v>
+        <v>41.9</v>
       </c>
       <c r="H188" t="n">
-        <v>7.29</v>
+        <v>11.24</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.93</v>
+        <v>-4.59</v>
       </c>
       <c r="J188" t="n">
-        <v>7.03</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7224,34 +7312,34 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>16.1</v>
+        <v>20.2</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.98pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 23.90pp)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G189" t="n">
-        <v>48.6</v>
+        <v>33.3</v>
       </c>
       <c r="H189" t="n">
-        <v>10.2</v>
+        <v>19.28</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.78</v>
+        <v>-4.62</v>
       </c>
       <c r="J189" t="n">
-        <v>8.300000000000001</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7260,38 +7348,34 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.12pp)</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
-        </is>
-      </c>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.90pp)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G190" t="n">
-        <v>44.1</v>
+        <v>35.9</v>
       </c>
       <c r="H190" t="n">
-        <v>7.72</v>
+        <v>6</v>
       </c>
       <c r="I190" t="n">
-        <v>-2.4</v>
+        <v>-3.9</v>
       </c>
       <c r="J190" t="n">
-        <v>5.8</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7300,34 +7384,34 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>14.7</v>
+        <v>20</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.14pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.28pp)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G191" t="n">
-        <v>39.5</v>
+        <v>28.6</v>
       </c>
       <c r="H191" t="n">
-        <v>6.02</v>
+        <v>2.16</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.12</v>
+        <v>-4.12</v>
       </c>
       <c r="J191" t="n">
-        <v>7.49</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7336,34 +7420,38 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>14.4</v>
+        <v>18.6</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.84pp)</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.17pp)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F192" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G192" t="n">
-        <v>43.6</v>
+        <v>32.4</v>
       </c>
       <c r="H192" t="n">
-        <v>9.91</v>
+        <v>0.22</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.93</v>
+        <v>-4.95</v>
       </c>
       <c r="J192" t="n">
-        <v>6.7</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7372,34 +7460,34 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>13.3</v>
+        <v>15.9</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 9.94pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.86pp)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G193" t="n">
-        <v>40</v>
+        <v>31.7</v>
       </c>
       <c r="H193" t="n">
-        <v>7.17</v>
+        <v>1.07</v>
       </c>
       <c r="I193" t="n">
-        <v>-2.77</v>
+        <v>-4.79</v>
       </c>
       <c r="J193" t="n">
-        <v>5.78</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7408,11 +7496,11 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.75pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.24pp)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7421,19 +7509,19 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G194" t="n">
-        <v>35.1</v>
+        <v>27.3</v>
       </c>
       <c r="H194" t="n">
-        <v>5.85</v>
+        <v>2.47</v>
       </c>
       <c r="I194" t="n">
-        <v>-1.9</v>
+        <v>-4.77</v>
       </c>
       <c r="J194" t="n">
-        <v>6.92</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="195">
@@ -7448,11 +7536,11 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>12.5</v>
+        <v>15.4</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.44pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 13.67pp)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7464,22 +7552,22 @@
         <v>25</v>
       </c>
       <c r="G195" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H195" t="n">
-        <v>13.92</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-1.52</v>
+        <v>-5.13</v>
       </c>
       <c r="J195" t="n">
-        <v>6.36</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7488,34 +7576,34 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>11.9</v>
+        <v>15.2</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.87pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 5.64pp)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G196" t="n">
-        <v>34.1</v>
+        <v>26.7</v>
       </c>
       <c r="H196" t="n">
-        <v>5.48</v>
+        <v>-1.01</v>
       </c>
       <c r="I196" t="n">
-        <v>-2.39</v>
+        <v>-6.65</v>
       </c>
       <c r="J196" t="n">
-        <v>6.67</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7524,34 +7612,38 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>9.5</v>
+        <v>14.7</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.03pp)</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.15pp)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F197" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G197" t="n">
-        <v>38.9</v>
+        <v>27</v>
       </c>
       <c r="H197" t="n">
-        <v>2.78</v>
+        <v>1.76</v>
       </c>
       <c r="I197" t="n">
-        <v>-4.25</v>
+        <v>-4.39</v>
       </c>
       <c r="J197" t="n">
-        <v>8.56</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7560,34 +7652,38 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 16.68pp)</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 16.12pp)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
       <c r="F198" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G198" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="H198" t="n">
-        <v>14.46</v>
+        <v>10.45</v>
       </c>
       <c r="I198" t="n">
-        <v>-2.22</v>
+        <v>-5.67</v>
       </c>
       <c r="J198" t="n">
-        <v>6.56</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7596,11 +7692,11 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>6.3</v>
+        <v>11.6</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 17.90pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 7.00pp)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7609,25 +7705,25 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G199" t="n">
-        <v>37.5</v>
+        <v>30.2</v>
       </c>
       <c r="H199" t="n">
-        <v>15.64</v>
+        <v>1.61</v>
       </c>
       <c r="I199" t="n">
-        <v>-2.26</v>
+        <v>-5.39</v>
       </c>
       <c r="J199" t="n">
-        <v>7.12</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7636,34 +7732,34 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>6</v>
+        <v>11.1</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 18.64pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.61pp)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G200" t="n">
-        <v>36.8</v>
+        <v>30.3</v>
       </c>
       <c r="H200" t="n">
-        <v>16.68</v>
+        <v>6.58</v>
       </c>
       <c r="I200" t="n">
-        <v>-1.96</v>
+        <v>-5.03</v>
       </c>
       <c r="J200" t="n">
-        <v>7.24</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7672,34 +7768,34 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4.9</v>
+        <v>7.5</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 11.84pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 6.95pp)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G201" t="n">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="H201" t="n">
-        <v>8.06</v>
+        <v>-2.39</v>
       </c>
       <c r="I201" t="n">
-        <v>-3.78</v>
+        <v>-9.34</v>
       </c>
       <c r="J201" t="n">
-        <v>11.66</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7708,34 +7804,34 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 15.19pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 16.42pp)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G202" t="n">
-        <v>37.9</v>
+        <v>30</v>
       </c>
       <c r="H202" t="n">
-        <v>11.62</v>
+        <v>11.16</v>
       </c>
       <c r="I202" t="n">
-        <v>-3.57</v>
+        <v>-5.26</v>
       </c>
       <c r="J202" t="n">
-        <v>7.64</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7744,28 +7840,140 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 12.04pp)</t>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 14.27pp)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="n">
+        <v>29</v>
+      </c>
+      <c r="G203" t="n">
+        <v>31</v>
+      </c>
+      <c r="H203" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="I203" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="J203" t="n">
+        <v>8.970000000000001</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.32pp)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
         <v>39</v>
       </c>
-      <c r="G203" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H203" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="I203" t="n">
-        <v>-4.23</v>
-      </c>
-      <c r="J203" t="n">
-        <v>9.09</v>
+      <c r="G204" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I204" t="n">
+        <v>-10.12</v>
+      </c>
+      <c r="J204" t="n">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 16.46pp)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="n">
+        <v>38</v>
+      </c>
+      <c r="G205" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H205" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I205" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="J205" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>⚠ RELIES ON OUTLIER WINS (avg-median gap 10.25pp)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>⚠ HIGH GAP RISK (&gt;10.0%)</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>36</v>
+      </c>
+      <c r="G206" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H206" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I206" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="J206" t="n">
+        <v>12.18</v>
       </c>
     </row>
   </sheetData>
